--- a/dicom-mri/v2.0.0/dicom-mri-v2.0.0.xlsx
+++ b/dicom-mri/v2.0.0/dicom-mri-v2.0.0.xlsx
@@ -42,10 +42,10 @@
     </comment>
     <comment ref="C1" authorId="1">
       <text>
-        <t>A locally assigned identifier provided by the data provider for the dataset. It
-is used to reference an external metadata record that may be maintained
-independently, enabling traceability and supporting provenance tracking.
-Example: Visium_9OLC_A4_S1</t>
+        <t>A local identifier assigned by the data provider to the dataset, used to
+reference an external metadata record that may be maintained independently,
+enabling traceability and supporting provenance tracking. Leave empty when the
+record has no such identifier for the dataset. Example: Visium_9OLC_A4_S1</t>
       </text>
     </comment>
     <comment ref="D1" authorId="1">
@@ -149,7 +149,7 @@
       <text>
         <t>Multiple images are acquired from regions of interest (ROI1, ROI2, ROI3, etc) on
 a slide. The ROI ID is a number from 1 to N representing the ROI captured on a
-slide. Example: ROI1</t>
+slide. Example: 1</t>
       </text>
     </comment>
     <comment ref="T1" authorId="1">
@@ -296,7 +296,7 @@
       <text>
         <t>(Required) The unique string identifier for the metadata specification version,
 which is easily interpretable by computers for purposes of data validation and
-processing. Example: 95b3a9bd-3fb3-48f5-99f8-1f78ffb6bb1d</t>
+processing. Example: f8c76a33-6262-4733-8f00-23175af7fd73</t>
       </text>
     </comment>
   </commentList>
@@ -507,7 +507,7 @@
     <t>pav:createdOn</t>
   </si>
   <si>
-    <t>2026-04-28T09:47:34-07:00</t>
+    <t>2026-10-21T13:38:10-07:00</t>
   </si>
   <si>
     <t>pav:derivedFrom</t>
